--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0002T0006Z000C1N25_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0002T0006Z000C1N25_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>33.35252306142259</v>
+        <v>5.41978499748117</v>
       </c>
       <c r="D2" t="n">
-        <v>21.50581316760657</v>
+        <v>3.494694639736068</v>
       </c>
       <c r="E2" t="n">
-        <v>9.047446559297327</v>
+        <v>1.470210065885816</v>
       </c>
       <c r="F2" t="n">
-        <v>13.63233335186639</v>
+        <v>2.215254169678289</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>19.9012752891078</v>
+        <v>3.233957234480018</v>
       </c>
       <c r="D3" t="n">
-        <v>20.99600447789834</v>
+        <v>3.41185072765848</v>
       </c>
       <c r="E3" t="n">
-        <v>9.047446559297327</v>
+        <v>1.470210065885816</v>
       </c>
       <c r="F3" t="n">
-        <v>13.63233335186639</v>
+        <v>2.215254169678289</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>17.97091944633596</v>
+        <v>2.920274410029593</v>
       </c>
       <c r="D4" t="n">
-        <v>17.6311996079177</v>
+        <v>2.865069936286627</v>
       </c>
       <c r="E4" t="n">
-        <v>9.047446559297327</v>
+        <v>1.470210065885816</v>
       </c>
       <c r="F4" t="n">
-        <v>13.63233335186639</v>
+        <v>2.215254169678289</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>35.23723422561904</v>
+        <v>5.726050561663095</v>
       </c>
       <c r="D5" t="n">
-        <v>49.05968013650169</v>
+        <v>7.972198022181525</v>
       </c>
       <c r="E5" t="n">
-        <v>9.047446559297327</v>
+        <v>1.470210065885816</v>
       </c>
       <c r="F5" t="n">
-        <v>13.63233335186639</v>
+        <v>2.215254169678289</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>45.24796209702762</v>
+        <v>7.352793840766988</v>
       </c>
       <c r="D6" t="n">
-        <v>50.22885401492166</v>
+        <v>8.16218877742477</v>
       </c>
       <c r="E6" t="n">
-        <v>9.047446559297327</v>
+        <v>1.470210065885816</v>
       </c>
       <c r="F6" t="n">
-        <v>13.63233335186639</v>
+        <v>2.215254169678289</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>27.17731451126048</v>
+        <v>4.416313608079829</v>
       </c>
       <c r="D7" t="n">
-        <v>25.93001609289234</v>
+        <v>4.213627615095005</v>
       </c>
       <c r="E7" t="n">
-        <v>9.047446559297327</v>
+        <v>1.470210065885816</v>
       </c>
       <c r="F7" t="n">
-        <v>13.63233335186639</v>
+        <v>2.215254169678289</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>36.81395341801763</v>
+        <v>5.982267430427865</v>
       </c>
       <c r="D8" t="n">
-        <v>9.816308425834576</v>
+        <v>1.595150119198119</v>
       </c>
       <c r="E8" t="n">
-        <v>9.047446559297327</v>
+        <v>1.470210065885816</v>
       </c>
       <c r="F8" t="n">
-        <v>13.63233335186639</v>
+        <v>2.215254169678289</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>30.71828927451127</v>
+        <v>4.991722007108082</v>
       </c>
       <c r="D9" t="n">
-        <v>9.677097032696393</v>
+        <v>1.572528267813164</v>
       </c>
       <c r="E9" t="n">
-        <v>9.047446559297327</v>
+        <v>1.470210065885816</v>
       </c>
       <c r="F9" t="n">
-        <v>13.63233335186639</v>
+        <v>2.215254169678289</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>25.42429709330062</v>
+        <v>4.131448277661351</v>
       </c>
       <c r="D10" t="n">
-        <v>25.10628061414246</v>
+        <v>4.07977059979815</v>
       </c>
       <c r="E10" t="n">
-        <v>9.047446559297327</v>
+        <v>1.470210065885816</v>
       </c>
       <c r="F10" t="n">
-        <v>13.63233335186639</v>
+        <v>2.215254169678289</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>14.3850900008387</v>
+        <v>2.337577125136289</v>
       </c>
       <c r="D11" t="n">
-        <v>15.16783005609707</v>
+        <v>2.464772384115774</v>
       </c>
       <c r="E11" t="n">
-        <v>9.047446559297327</v>
+        <v>1.470210065885816</v>
       </c>
       <c r="F11" t="n">
-        <v>13.63233335186639</v>
+        <v>2.215254169678289</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
